--- a/Result/profitability/9926.xlsx
+++ b/Result/profitability/9926.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6175</v>
+        <v>0.64</v>
       </c>
       <c r="N2" t="n">
-        <v>24.95875</v>
+        <v>24.7675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6075</v>
+        <v>0.68125</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2425</v>
+        <v>25.02</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6212500000000001</v>
+        <v>0.6575</v>
       </c>
       <c r="N4" t="n">
-        <v>24.41125</v>
+        <v>24.68875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>0.60125</v>
+        <v>0.6162500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>23.9075</v>
+        <v>23.66375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5725</v>
+        <v>0.5825</v>
       </c>
       <c r="N6" t="n">
-        <v>22.8525</v>
+        <v>22.74125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.53625</v>
+        <v>0.60375</v>
       </c>
       <c r="N7" t="n">
-        <v>22.47875</v>
+        <v>23.19875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.56375</v>
+        <v>0.5950000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>23.1175</v>
+        <v>23.28375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.55</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>22.01</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>619</v>
+      </c>
+      <c r="D75" t="n">
+        <v>448</v>
+      </c>
+      <c r="E75" t="n">
+        <v>170</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>109</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>84</v>
+      </c>
+      <c r="J75" t="n">
+        <v>193</v>
+      </c>
+      <c r="K75" t="n">
+        <v>166</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6737500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.115</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3676470588235294</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.330000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05080213903743314</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.949999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06619144602851323</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
